--- a/storage/Accounting_Ledger.xlsx
+++ b/storage/Accounting_Ledger.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>TANGGAL</t>
   </si>
@@ -35,6 +35,12 @@
   </si>
   <si>
     <t>Import Invoice Invoice</t>
+  </si>
+  <si>
+    <t>0001/INV-FDL/I/2026</t>
+  </si>
+  <si>
+    <t>PT. Mercury Tekindo Internusa</t>
   </si>
 </sst>
 </file>
@@ -45,7 +51,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* (#,##0);_(&quot;Rp&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -57,6 +63,9 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="3">
@@ -91,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -100,6 +109,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -530,6 +554,26 @@
         <v>1045000</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>46052</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="8">
+        <v>44500000</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9">
+        <v>45545000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/storage/Accounting_Ledger.xlsx
+++ b/storage/Accounting_Ledger.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
   <si>
     <t>TANGGAL</t>
   </si>
@@ -41,6 +41,72 @@
   </si>
   <si>
     <t>PT. Mercury Tekindo Internusa</t>
+  </si>
+  <si>
+    <t>0002/INV-FDL/I/2026</t>
+  </si>
+  <si>
+    <t>vdhasda</t>
+  </si>
+  <si>
+    <t>0115/INV-FDL/I/2026</t>
+  </si>
+  <si>
+    <t>dadas</t>
+  </si>
+  <si>
+    <t>0002/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0003/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0004/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>sadasd</t>
+  </si>
+  <si>
+    <t>0005/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0007/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0008/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0009/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0010/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0011/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0012/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0013/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0014/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>sdaasd</t>
+  </si>
+  <si>
+    <t>0015/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>0016/INV-FDL/II/2026</t>
+  </si>
+  <si>
+    <t>sadas</t>
+  </si>
+  <si>
+    <t>0018/INV-FDL/II/2026</t>
   </si>
 </sst>
 </file>
@@ -464,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -574,6 +640,386 @@
         <v>45545000</v>
       </c>
     </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>46052</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="8">
+        <v>25000</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
+        <v>45570000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="8">
+        <v>2043676</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9">
+        <v>47613676</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="8">
+        <v>9092909</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
+        <v>56706585</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="8">
+        <v>135096194</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <v>191802779</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="8">
+        <v>356487745</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>548290524</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="8">
+        <v>342424</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9">
+        <v>548632948</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1022238</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>549655186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="8">
+        <v>6776864</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9">
+        <v>556432050</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="8">
+        <v>8335342</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>564767392</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="8">
+        <v>35404324</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9">
+        <v>600171716</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="8">
+        <v>7436533</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>607608249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="8">
+        <v>324234</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9">
+        <v>607932483</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="8">
+        <v>45322</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>607977805</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="8">
+        <v>324342</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="9">
+        <v>608302147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="8">
+        <v>3790999</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>612093146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="8">
+        <v>37272944</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>649366090</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="8">
+        <v>691201420</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1340567510</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="8">
+        <v>9063143</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1349630653</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="5">
+        <v>46054</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="8">
+        <v>233120</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0</v>
+      </c>
+      <c r="F24" s="9">
+        <v>1349863773</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/storage/Accounting_Ledger.xlsx
+++ b/storage/Accounting_Ledger.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
     <t>TANGGAL</t>
   </si>
@@ -530,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -1020,6 +1020,26 @@
         <v>1349863773</v>
       </c>
     </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>46054</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="4">
+        <v>165000</v>
+      </c>
+      <c r="E25" s="4">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1350028773</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
